--- a/reportes/RESULTADOS_EXPERIMENTO_GRUPO4.xlsx
+++ b/reportes/RESULTADOS_EXPERIMENTO_GRUPO4.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
@@ -74,14 +78,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -451,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -505,7 +510,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMD64 Family 23 Model 113 Stepping 0, AuthenticAMD</t>
+          <t>AMD Ryzen 7 3700X, 8 nucleos, 3,6 GHz (AMD64 Family 23 Model 113 Stepping 0, AuthenticAMD)</t>
         </is>
       </c>
     </row>
@@ -517,81 +522,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+          <t>32 GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Datos de la maquina del experimento (fijos). No se detecta el equipo donde corre el script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>PARÁMETROS DEL ALGORITMO EVOLUTIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Tamaño de Población:</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>50 individuos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Generaciones:</t>
+          <t>Tamaño de Población:</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100 generaciones</t>
+          <t>50 individuos</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Elitismo:</t>
+          <t>Generaciones:</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2 individuos</t>
+          <t>100 generaciones</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Probabilidad Crossover:</t>
+          <t>Elitismo:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>2 individuos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Probabilidad Mutación (Subtree):</t>
+          <t>Probabilidad Crossover:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>70%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Probabilidad Mutación (One Node):</t>
+          <t>Probabilidad Mutación (Subtree):</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -603,150 +603,162 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Probabilidad Mutación (One Node):</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Selección:</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Tournament Selection (tamaño 4)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>INSTANCIAS DE EVALUACIÓN</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Número de Instancias:</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>8 instancias</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>(Las primeras N de data/evolution según experiment.max.instances; cada individuo se evalúa con todas ellas)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>FITNESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fitness Estandarizado:</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Error Relativo Promedio (ERP)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fitness Ajustado:</t>
+          <t>Fitness Estandarizado:</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1 / (1 + Fitness Estandarizado)</t>
+          <t>Error Relativo Promedio (ERP)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fitness Usado:</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Fitness Estandarizado (ERP)</t>
+          <t>Fitness Ajustado:</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1 / (1 + Fitness Estandarizado)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ERP (Error Relativo Promedio):</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Promedio del error relativo de todas las instancias</t>
+          <t>Fitness Usado:</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Fitness Estandarizado (ERP)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>ERP (Error Relativo Promedio):</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Promedio del error relativo de todas las instancias</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Error Relativo por Instancia:</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>|óptimo - solución_obtenida| / óptimo</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>NOTAS IMPORTANTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>• Los 'Individuos' en 'Estadísticas por Ejecución' son el total de individuos evaluados durante toda la ejecución (no el tamaño de población)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>• El 'Best Fitness' es del MEJOR individuo de cada generación</t>
+          <t>• Los 'Individuos' en 'Estadísticas por Ejecución' son el total de individuos evaluados durante toda la ejecución (no el tamaño de población)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>• 'AvgERP' es el Error Relativo Promedio de TODA la población en esa generación</t>
+          <t>• El 'Best Fitness' es del MEJOR individuo de cada generación</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>• 'BestERP' es el Error Relativo Promedio del MEJOR individuo de esa generación</t>
+          <t>• 'AvgERP' es el Error Relativo Promedio de TODA la población en esa generación</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>• Cada individuo se evalúa con 8 instancias de prueba</t>
+          <t>• 'BestERP' es el Error Relativo Promedio del MEJOR individuo de esa generación</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>• Cada individuo se evalúa con 8 instancias de prueba</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>• El formato de números usa punto (.) como separador decimal (formato inglés)</t>
         </is>
@@ -760,7 +772,7 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -772,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -795,179 +807,223 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Promedio:</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1171.938 segundos</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>(sobre las 8 instancias del protocolo)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mínimo:</t>
+          <t>Total:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.080 segundos</t>
+          <t>581.675 segundos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Máximo:</t>
+          <t>Promedio:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23971.809 segundos</t>
+          <t>72.709 segundos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Mínimo:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4.194 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Máximo:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>169.439 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Desviación Estándar:</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3903.620 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>65.783 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>ESTADISTICAS CONSOLIDADAS (Todas las Ejecuciones)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Total Ejecuciones:</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Total Individuos Evaluados:</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>45589</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>(Suma de todos los individuos evaluados en todas las ejecuciones)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total Llamadas CPLEX:</t>
+          <t>Total Ejecuciones:</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1457942</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tiempo Total CPLEX:</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>8386583.66 segundos</t>
+          <t>Total Individuos Evaluados:</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>(generaciones x poblacion, sumado sobre las ejecuciones)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Presupuesto CPLEX:</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>75.0% del baseline por instancia</t>
+          <t>Individuos con llamadas a CPLEX:</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13141</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>(individuos que invocaron el terminal exacto al menos una vez)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total Llamadas CPLEX:</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>500267</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>(suma de las ejecuciones; fuente: CplexUsage.detailed.csv)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>RENDIMIENTO EVOLUTIVO (Generación Final)</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tiempo Total CPLEX:</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2794758.59 segundos</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>(CPU del solver, suma de las ejecuciones)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mejor ERP Promedio:</t>
+          <t>Presupuesto CPLEX:</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.001777</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>(Promedio del mejor ERP de cada ejecución)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ERP Poblacional Promedio:</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.171940</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>(Promedio del ERP de la población en cada ejecución)</t>
+          <t>75.0% del baseline por instancia</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Mejor Fitness Promedio:</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.001777</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RENDIMIENTO EVOLUTIVO (Generación Final)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Mejor ERP Promedio:</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.001777</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>(Promedio del mejor ERP de cada ejecución)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ERP Poblacional Promedio:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.171940</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>(Promedio del ERP de la población en cada ejecución)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mejor Fitness Promedio:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.001777</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Fitness Poblacional Promedio:</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>0.171940</t>
         </is>
@@ -987,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -995,39 +1051,45 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>NOTA: Estos tiempos fueron obtenidos resolviendo cada instancia con CPLEX puro (sin programación genética). Ver información de la máquina en la hoja 'Configuración'.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Instancia</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Tiempo Baseline (s)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Clientes/Nodos</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Capacidad/Variante</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Usada en el protocolo</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1099,7 @@
           <t>Mitra-1-16.txt</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>0.08013000000000001</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -1053,6 +1115,11 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1129,7 @@
           <t>Mitra-1-01.txt</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="7" t="n">
         <v>0.187251</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -1078,6 +1145,11 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1159,7 @@
           <t>Mitra-1-02.txt</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>0.224259</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -1103,6 +1175,11 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>02</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1189,7 @@
           <t>R161_15_80.txt</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>0.412618</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -1128,6 +1205,11 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>Capacidad: 80</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1219,7 @@
           <t>Mitra-1-06.txt</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>0.41276</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -1153,6 +1235,11 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>06</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1249,7 @@
           <t>R161_17_80.txt</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>0.414657</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -1178,6 +1265,11 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>Capacidad: 80</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1279,7 @@
           <t>R141_15_120.txt</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>0.442656</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1203,6 +1295,11 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1309,7 @@
           <t>R121_15_120.txt</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>0.554284</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1228,6 +1325,11 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1339,7 @@
           <t>R121_15_80.txt</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>0.649007</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1253,6 +1355,11 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>Capacidad: 80</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1369,7 @@
           <t>R161_17_120.txt</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>0.671078</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1278,6 +1385,11 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1399,7 @@
           <t>Mitra-2-02.txt</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>0.688319</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1303,6 +1415,11 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>02</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1429,7 @@
           <t>Mitra-2-06.txt</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <v>0.755782</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1328,6 +1445,11 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>06</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1459,7 @@
           <t>R141_17_120.txt</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>0.799944</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1353,6 +1475,11 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1489,7 @@
           <t>R141_17_80.txt</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>0.93367</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1378,6 +1505,11 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>Capacidad: 80</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1519,7 @@
           <t>R161_15_120.txt</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="7" t="n">
         <v>0.989488</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1403,6 +1535,11 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1549,7 @@
           <t>R141_15_80.txt</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="7" t="n">
         <v>1.188191</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1428,6 +1565,11 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>Capacidad: 80</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1579,7 @@
           <t>R121_17_120.txt</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="7" t="n">
         <v>1.315274</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1453,6 +1595,11 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1609,7 @@
           <t>R141_20_120.txt</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="7" t="n">
         <v>1.505476</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1478,6 +1625,11 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1639,7 @@
           <t>Mitra-2-16.txt</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="7" t="n">
         <v>1.542257</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1503,6 +1655,11 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1669,7 @@
           <t>3C_20_50-01.txt</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="7" t="n">
         <v>3.886491</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1528,6 +1685,11 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>Capacidad: 50, Variante: 01</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1699,7 @@
           <t>3C_20_80-01.txt</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="7" t="n">
         <v>4.194486</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1553,6 +1715,11 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>Capacidad: 80, Variante: 01</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1729,7 @@
           <t>R101_20_02.txt</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="7" t="n">
         <v>4.425208</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1578,6 +1745,11 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>Capacidad: 02</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1759,7 @@
           <t>R121_20_120.txt</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="7" t="n">
         <v>5.255634</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1603,6 +1775,11 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>Capacidad: 120</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1789,7 @@
           <t>3C_20_66-01.txt</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="7" t="n">
         <v>7.322185</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1628,6 +1805,11 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>Capacidad: 66, Variante: 01</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1819,7 @@
           <t>R121_17_80.txt</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="7" t="n">
         <v>13.320136</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1653,6 +1835,11 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>Capacidad: 80</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1849,7 @@
           <t>R101_20_08.txt</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="7" t="n">
         <v>22.899316</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1678,6 +1865,11 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>Capacidad: 08</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1879,7 @@
           <t>Mitra-2-01.txt</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="7" t="n">
         <v>23.287018</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1703,6 +1895,11 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>01</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1909,7 @@
           <t>3C_20_50-03.txt</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="7" t="n">
         <v>30.992571</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1728,6 +1925,11 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>Capacidad: 50, Variante: 03</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1939,7 @@
           <t>C101_20_08.txt</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="7" t="n">
         <v>32.551019</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1753,6 +1955,11 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>Variante: 08</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1969,7 @@
           <t>RC101_20_08.txt</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="7" t="n">
         <v>35.054967</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1778,6 +1985,11 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>Variante: 08</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1999,7 @@
           <t>3C_20_80-02.txt</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="7" t="n">
         <v>35.738139</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1803,6 +2015,11 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>Capacidad: 80, Variante: 02</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1812,7 +2029,7 @@
           <t>RC101_20_02.txt</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="7" t="n">
         <v>60.026389</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1828,6 +2045,11 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>Variante: 02</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1837,7 +2059,7 @@
           <t>3C_20_50-02.txt</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="7" t="n">
         <v>61.404368</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -1853,6 +2075,11 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>Capacidad: 50, Variante: 02</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1862,7 +2089,7 @@
           <t>3C_20_66-03.txt</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="7" t="n">
         <v>118.339569</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -1878,6 +2105,11 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>Capacidad: 66, Variante: 03</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1887,7 +2119,7 @@
           <t>3C_20_66-02.txt</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="7" t="n">
         <v>154.244889</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -1903,6 +2135,11 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>Capacidad: 66, Variante: 02</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1912,7 +2149,7 @@
           <t>3C_20_80-03.txt</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="7" t="n">
         <v>169.438998</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -1928,6 +2165,11 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>Capacidad: 80, Variante: 03</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1937,7 +2179,7 @@
           <t>C101_20_02.txt</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="7" t="n">
         <v>217.381347</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -1953,6 +2195,11 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>Variante: 02</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1962,7 +2209,7 @@
           <t>3C_40_80-01.txt</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="7" t="n">
         <v>302.092888</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -1978,6 +2225,11 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>Capacidad: 80, Variante: 01</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1987,7 +2239,7 @@
           <t>SCA3-2.txt</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="7" t="n">
         <v>1515.516945</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2003,6 +2255,11 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2269,7 @@
           <t>3C_40_66-01.txt</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="7" t="n">
         <v>1964.052109</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2028,6 +2285,11 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>Capacidad: 66, Variante: 01</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2299,7 @@
           <t>CON3-3.txt</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="7" t="n">
         <v>1983.202089</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2053,6 +2315,11 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2329,7 @@
           <t>CMT1y.txt</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="7" t="n">
         <v>2950.052655</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2078,6 +2345,11 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2359,7 @@
           <t>SCA3-3.txt</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="7" t="n">
         <v>3579.34089</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2103,6 +2375,11 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2389,7 @@
           <t>CMT1x.txt</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="7" t="n">
         <v>6872.507343</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2128,6 +2405,11 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2419,7 @@
           <t>CON3-0.txt</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="7" t="n">
         <v>9757.060086</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2153,6 +2435,11 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2449,7 @@
           <t>SCA3-5.txt</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="7" t="n">
         <v>23971.809037</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2178,6 +2465,11 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2204,44 +2496,50 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>NOTA IMPORTANTE: 'Individuos Evaluados' = Total acumulado de individuos evaluados durante TODA la ejecución (100 generaciones). NO es el tamaño de población (que es 50). 'Llamadas CPLEX' = Total de llamadas a CPLEX durante toda la ejecución. 'Tiempo Total' = Tiempo total en segundos usado por CPLEX en toda la ejecución.</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>NOTA: valores POR EJECUCION calculados desde job.M.CplexUsage.detailed.csv (una fila por llamada). 'Individuos Evaluados' = generaciones x poblacion (100 x 50 = 5000). 'Individuos con llamadas CPLEX' = individuos que invocaron el terminal exacto al menos una vez. 'Llamadas CPLEX (Total)' = filas del registro. 'Tiempo Total CPLEX (s)' = suma de TimeUsed (CPU del solver, ClockType=1, Threads=2). Los promedios por individuo dividen por los individuos evaluados. NO se usa job.M.CplexUsage.statistics.txt: acumula entre los jobs de la misma JVM (valores inflados en versiones anteriores de este Excel).</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Ejecución</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Individuos Evaluados</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Llamadas CPLEX (Total)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Tiempo Total CPLEX (s)</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Prom. Llamadas/Indiv</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Prom. Tiempo/Indiv (s)</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Individuos con llamadas CPLEX</t>
         </is>
       </c>
     </row>
@@ -2250,19 +2548,22 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>3241</v>
+        <v>5000</v>
       </c>
       <c r="C3" t="n">
-        <v>89915</v>
+        <v>89925</v>
       </c>
       <c r="D3" t="n">
-        <v>562767.563</v>
+        <v>562771.733</v>
       </c>
       <c r="E3" t="n">
-        <v>27.74</v>
+        <v>17.985</v>
       </c>
       <c r="F3" t="n">
-        <v>173.64</v>
+        <v>112.554</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2286</v>
       </c>
     </row>
     <row r="4">
@@ -2270,19 +2571,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>6092</v>
+        <v>5000</v>
       </c>
       <c r="C4" t="n">
-        <v>191927</v>
+        <v>102055</v>
       </c>
       <c r="D4" t="n">
-        <v>1228142.078</v>
+        <v>665379.749</v>
       </c>
       <c r="E4" t="n">
-        <v>31.5</v>
+        <v>20.411</v>
       </c>
       <c r="F4" t="n">
-        <v>201.599</v>
+        <v>133.076</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2541</v>
       </c>
     </row>
     <row r="5">
@@ -2290,19 +2594,22 @@
         <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>9143</v>
+        <v>5000</v>
       </c>
       <c r="C5" t="n">
-        <v>286979</v>
+        <v>95245</v>
       </c>
       <c r="D5" t="n">
-        <v>1594449.641</v>
+        <v>366311.425</v>
       </c>
       <c r="E5" t="n">
-        <v>31.39</v>
+        <v>19.049</v>
       </c>
       <c r="F5" t="n">
-        <v>174.39</v>
+        <v>73.262</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2958</v>
       </c>
     </row>
     <row r="6">
@@ -2310,19 +2617,22 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>12142</v>
+        <v>5000</v>
       </c>
       <c r="C6" t="n">
-        <v>389319</v>
+        <v>102371</v>
       </c>
       <c r="D6" t="n">
-        <v>2206488.063</v>
+        <v>612042.943</v>
       </c>
       <c r="E6" t="n">
-        <v>32.06</v>
+        <v>20.474</v>
       </c>
       <c r="F6" t="n">
-        <v>181.724</v>
+        <v>122.409</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2635</v>
       </c>
     </row>
     <row r="7">
@@ -2330,24 +2640,27 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>14971</v>
+        <v>5000</v>
       </c>
       <c r="C7" t="n">
-        <v>499802</v>
+        <v>110671</v>
       </c>
       <c r="D7" t="n">
-        <v>2794736.313</v>
+        <v>588252.736</v>
       </c>
       <c r="E7" t="n">
-        <v>33.38</v>
+        <v>22.134</v>
       </c>
       <c r="F7" t="n">
-        <v>186.677</v>
+        <v>117.651</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2721</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2370,34 +2683,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>NOTA IMPORTANTE: Estos son los valores del MEJOR individuo de cada generación. Fitness Estandarizado = ERP (Error Relativo Promedio sobre todas las instancias). Fitness Ajustado = 1/(1+ERP). El fitness que se usa para la selección es el ESTANDARIZADO (ERP). Cada individuo se evalúa con todas las instancias de prueba.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Ejecución</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Generación</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Fitness Estandarizado (ERP)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Fitness Ajustado</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
@@ -10933,59 +11246,59 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>NOTA IMPORTANTE: AvgERP = Error Relativo Promedio (ERP) de TODA la población en esa generación. BestERP = Error Relativo Promedio (ERP) del MEJOR individuo de esa generación. Cada individuo se evalúa con 8 instancias de prueba. El ERP se calcula como: promedio de |óptimo - solución| / óptimo sobre todas las instancias.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Ejecución</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Gen</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>AvgSize</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>AvgERP</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>AvgFitness</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>BestSize</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>BestERP</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>BestFitness</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>AvgHits</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>BestHits</t>
         </is>
